--- a/docs/StructureDefinition-NoImplVitalSignsObservationGCS.xlsx
+++ b/docs/StructureDefinition-NoImplVitalSignsObservationGCS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:16:58+00:00</t>
+    <t>2026-09-08T11:30:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1303,7 +1303,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://dips.no/fhir/R4/StructureDefinition/DIPSPatient)
+    <t xml:space="preserve">Reference(http://dips.no/fhir/StructureDefinition/R4/DIPSPatient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-NoImplVitalSignsObservationGCS.xlsx
+++ b/docs/StructureDefinition-NoImplVitalSignsObservationGCS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:30:20+00:00</t>
+    <t>2026-09-15T05:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
